--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3667"/>
+  <dimension ref="A1:F3668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73767,6 +73767,26 @@
         <v>1708640</v>
       </c>
     </row>
+    <row r="3668">
+      <c r="A3668" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B3668" t="n">
+        <v>5122.5</v>
+      </c>
+      <c r="C3668" t="n">
+        <v>5135</v>
+      </c>
+      <c r="D3668" t="n">
+        <v>5116.5</v>
+      </c>
+      <c r="E3668" t="n">
+        <v>5130.5</v>
+      </c>
+      <c r="F3668" t="n">
+        <v>623748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -73778,13 +73778,13 @@
         <v>5135</v>
       </c>
       <c r="D3668" t="n">
-        <v>5116.5</v>
+        <v>5114</v>
       </c>
       <c r="E3668" t="n">
-        <v>5130.5</v>
+        <v>5123</v>
       </c>
       <c r="F3668" t="n">
-        <v>623748</v>
+        <v>1374294</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -73781,10 +73781,10 @@
         <v>5114</v>
       </c>
       <c r="E3668" t="n">
-        <v>5123</v>
+        <v>5131</v>
       </c>
       <c r="F3668" t="n">
-        <v>1374294</v>
+        <v>1639568</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -73781,10 +73781,10 @@
         <v>5114</v>
       </c>
       <c r="E3668" t="n">
-        <v>5131</v>
+        <v>5124.904</v>
       </c>
       <c r="F3668" t="n">
-        <v>1639568</v>
+        <v>1640943</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3668"/>
+  <dimension ref="A1:F3669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73787,6 +73787,26 @@
         <v>1640943</v>
       </c>
     </row>
+    <row r="3669">
+      <c r="A3669" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B3669" t="n">
+        <v>5128.5</v>
+      </c>
+      <c r="C3669" t="n">
+        <v>5144.5</v>
+      </c>
+      <c r="D3669" t="n">
+        <v>5110</v>
+      </c>
+      <c r="E3669" t="n">
+        <v>5125.5</v>
+      </c>
+      <c r="F3669" t="n">
+        <v>2003905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -73798,13 +73798,13 @@
         <v>5144.5</v>
       </c>
       <c r="D3669" t="n">
-        <v>5110</v>
+        <v>5091.5</v>
       </c>
       <c r="E3669" t="n">
-        <v>5125.5</v>
+        <v>5121.5</v>
       </c>
       <c r="F3669" t="n">
-        <v>2003905</v>
+        <v>2829376</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3669"/>
+  <dimension ref="A1:F3670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73801,10 +73801,30 @@
         <v>5091.5</v>
       </c>
       <c r="E3669" t="n">
-        <v>5121.5</v>
+        <v>5101.305</v>
       </c>
       <c r="F3669" t="n">
-        <v>2829376</v>
+        <v>2842466</v>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B3670" t="n">
+        <v>5107.5</v>
+      </c>
+      <c r="C3670" t="n">
+        <v>5109</v>
+      </c>
+      <c r="D3670" t="n">
+        <v>5060</v>
+      </c>
+      <c r="E3670" t="n">
+        <v>5067.5</v>
+      </c>
+      <c r="F3670" t="n">
+        <v>2008493</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3670"/>
+  <dimension ref="A1:F3671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73821,10 +73821,30 @@
         <v>5060</v>
       </c>
       <c r="E3670" t="n">
-        <v>5067.5</v>
+        <v>5071.993</v>
       </c>
       <c r="F3670" t="n">
         <v>2008493</v>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B3671" t="n">
+        <v>5115</v>
+      </c>
+      <c r="C3671" t="n">
+        <v>5119.5</v>
+      </c>
+      <c r="D3671" t="n">
+        <v>5101</v>
+      </c>
+      <c r="E3671" t="n">
+        <v>5117</v>
+      </c>
+      <c r="F3671" t="n">
+        <v>881706</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3671"/>
+  <dimension ref="A1:F3672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73841,10 +73841,30 @@
         <v>5101</v>
       </c>
       <c r="E3671" t="n">
-        <v>5117</v>
+        <v>5110.795</v>
       </c>
       <c r="F3671" t="n">
         <v>881706</v>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B3672" t="n">
+        <v>5107</v>
+      </c>
+      <c r="C3672" t="n">
+        <v>5127</v>
+      </c>
+      <c r="D3672" t="n">
+        <v>5087</v>
+      </c>
+      <c r="E3672" t="n">
+        <v>5123.5</v>
+      </c>
+      <c r="F3672" t="n">
+        <v>1501884</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3672"/>
+  <dimension ref="A1:F3673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73861,10 +73861,30 @@
         <v>5087</v>
       </c>
       <c r="E3672" t="n">
-        <v>5123.5</v>
+        <v>5122.488</v>
       </c>
       <c r="F3672" t="n">
         <v>1501884</v>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B3673" t="n">
+        <v>5108.5</v>
+      </c>
+      <c r="C3673" t="n">
+        <v>5181.5</v>
+      </c>
+      <c r="D3673" t="n">
+        <v>5105</v>
+      </c>
+      <c r="E3673" t="n">
+        <v>5157</v>
+      </c>
+      <c r="F3673" t="n">
+        <v>2137274</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3673"/>
+  <dimension ref="A1:F3674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73881,10 +73881,30 @@
         <v>5105</v>
       </c>
       <c r="E3673" t="n">
-        <v>5157</v>
+        <v>5171.47</v>
       </c>
       <c r="F3673" t="n">
         <v>2137274</v>
+      </c>
+    </row>
+    <row r="3674">
+      <c r="A3674" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B3674" t="n">
+        <v>5147</v>
+      </c>
+      <c r="C3674" t="n">
+        <v>5166</v>
+      </c>
+      <c r="D3674" t="n">
+        <v>5130</v>
+      </c>
+      <c r="E3674" t="n">
+        <v>5152</v>
+      </c>
+      <c r="F3674" t="n">
+        <v>1708986</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3674"/>
+  <dimension ref="A1:F3675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73901,10 +73901,30 @@
         <v>5130</v>
       </c>
       <c r="E3674" t="n">
-        <v>5152</v>
+        <v>5155.63</v>
       </c>
       <c r="F3674" t="n">
         <v>1708986</v>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B3675" t="n">
+        <v>5152</v>
+      </c>
+      <c r="C3675" t="n">
+        <v>5158.5</v>
+      </c>
+      <c r="D3675" t="n">
+        <v>5121</v>
+      </c>
+      <c r="E3675" t="n">
+        <v>5131.638</v>
+      </c>
+      <c r="F3675" t="n">
+        <v>1571420</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3675"/>
+  <dimension ref="A1:F3676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73927,6 +73927,26 @@
         <v>1571420</v>
       </c>
     </row>
+    <row r="3676">
+      <c r="A3676" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B3676" t="n">
+        <v>5129.5</v>
+      </c>
+      <c r="C3676" t="n">
+        <v>5132.5</v>
+      </c>
+      <c r="D3676" t="n">
+        <v>5102.5</v>
+      </c>
+      <c r="E3676" t="n">
+        <v>5110</v>
+      </c>
+      <c r="F3676" t="n">
+        <v>1736000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3676"/>
+  <dimension ref="A1:F3677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73941,10 +73941,30 @@
         <v>5102.5</v>
       </c>
       <c r="E3676" t="n">
-        <v>5110</v>
+        <v>5112.252</v>
       </c>
       <c r="F3676" t="n">
         <v>1736000</v>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B3677" t="n">
+        <v>5110</v>
+      </c>
+      <c r="C3677" t="n">
+        <v>5147</v>
+      </c>
+      <c r="D3677" t="n">
+        <v>5109.5</v>
+      </c>
+      <c r="E3677" t="n">
+        <v>5133</v>
+      </c>
+      <c r="F3677" t="n">
+        <v>1371679</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3677"/>
+  <dimension ref="A1:F3678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73961,10 +73961,30 @@
         <v>5109.5</v>
       </c>
       <c r="E3677" t="n">
-        <v>5133</v>
+        <v>5138.858</v>
       </c>
       <c r="F3677" t="n">
         <v>1371679</v>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B3678" t="n">
+        <v>5130</v>
+      </c>
+      <c r="C3678" t="n">
+        <v>5202.5</v>
+      </c>
+      <c r="D3678" t="n">
+        <v>5122.5</v>
+      </c>
+      <c r="E3678" t="n">
+        <v>5183.5</v>
+      </c>
+      <c r="F3678" t="n">
+        <v>2524037</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3678"/>
+  <dimension ref="A1:F3679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73981,10 +73981,30 @@
         <v>5122.5</v>
       </c>
       <c r="E3678" t="n">
-        <v>5183.5</v>
+        <v>5195.566</v>
       </c>
       <c r="F3678" t="n">
         <v>2524037</v>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B3679" t="n">
+        <v>5174</v>
+      </c>
+      <c r="C3679" t="n">
+        <v>5216</v>
+      </c>
+      <c r="D3679" t="n">
+        <v>5159</v>
+      </c>
+      <c r="E3679" t="n">
+        <v>5214</v>
+      </c>
+      <c r="F3679" t="n">
+        <v>2289925</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3679"/>
+  <dimension ref="A1:F3680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74001,10 +74001,30 @@
         <v>5159</v>
       </c>
       <c r="E3679" t="n">
-        <v>5214</v>
+        <v>5184.42</v>
       </c>
       <c r="F3679" t="n">
         <v>2289925</v>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3680" t="n">
+        <v>5208.5</v>
+      </c>
+      <c r="C3680" t="n">
+        <v>5221</v>
+      </c>
+      <c r="D3680" t="n">
+        <v>5197</v>
+      </c>
+      <c r="E3680" t="n">
+        <v>5204</v>
+      </c>
+      <c r="F3680" t="n">
+        <v>1979723</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3680"/>
+  <dimension ref="A1:F3681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74021,10 +74021,30 @@
         <v>5197</v>
       </c>
       <c r="E3680" t="n">
-        <v>5204</v>
+        <v>5209.946</v>
       </c>
       <c r="F3680" t="n">
         <v>1979723</v>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B3681" t="n">
+        <v>5192.5</v>
+      </c>
+      <c r="C3681" t="n">
+        <v>5268.5</v>
+      </c>
+      <c r="D3681" t="n">
+        <v>5192</v>
+      </c>
+      <c r="E3681" t="n">
+        <v>5234</v>
+      </c>
+      <c r="F3681" t="n">
+        <v>2717401</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3681"/>
+  <dimension ref="A1:F3682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74041,10 +74041,30 @@
         <v>5192</v>
       </c>
       <c r="E3681" t="n">
-        <v>5234</v>
+        <v>5245.327</v>
       </c>
       <c r="F3681" t="n">
-        <v>2717401</v>
+        <v>2717439</v>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B3682" t="n">
+        <v>5233.5</v>
+      </c>
+      <c r="C3682" t="n">
+        <v>5240</v>
+      </c>
+      <c r="D3682" t="n">
+        <v>5198.5</v>
+      </c>
+      <c r="E3682" t="n">
+        <v>5222</v>
+      </c>
+      <c r="F3682" t="n">
+        <v>1893774</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3682"/>
+  <dimension ref="A1:F3683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74044,7 +74044,7 @@
         <v>5245.327</v>
       </c>
       <c r="F3681" t="n">
-        <v>2717439</v>
+        <v>2717420</v>
       </c>
     </row>
     <row r="3682">
@@ -74061,10 +74061,30 @@
         <v>5198.5</v>
       </c>
       <c r="E3682" t="n">
-        <v>5222</v>
+        <v>5217.049</v>
       </c>
       <c r="F3682" t="n">
         <v>1893774</v>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B3683" t="n">
+        <v>5224</v>
+      </c>
+      <c r="C3683" t="n">
+        <v>5239</v>
+      </c>
+      <c r="D3683" t="n">
+        <v>5206</v>
+      </c>
+      <c r="E3683" t="n">
+        <v>5230</v>
+      </c>
+      <c r="F3683" t="n">
+        <v>1845463</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3683"/>
+  <dimension ref="A1:F3684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74081,10 +74081,30 @@
         <v>5206</v>
       </c>
       <c r="E3683" t="n">
-        <v>5230</v>
+        <v>5234.735</v>
       </c>
       <c r="F3683" t="n">
         <v>1845463</v>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3684" t="n">
+        <v>5221.5</v>
+      </c>
+      <c r="C3684" t="n">
+        <v>5225</v>
+      </c>
+      <c r="D3684" t="n">
+        <v>5170</v>
+      </c>
+      <c r="E3684" t="n">
+        <v>5193</v>
+      </c>
+      <c r="F3684" t="n">
+        <v>2197188</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3684"/>
+  <dimension ref="A1:F3685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74101,10 +74101,30 @@
         <v>5170</v>
       </c>
       <c r="E3684" t="n">
-        <v>5193</v>
+        <v>5182.067</v>
       </c>
       <c r="F3684" t="n">
         <v>2197188</v>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B3685" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C3685" t="n">
+        <v>5214.5</v>
+      </c>
+      <c r="D3685" t="n">
+        <v>5190</v>
+      </c>
+      <c r="E3685" t="n">
+        <v>5207</v>
+      </c>
+      <c r="F3685" t="n">
+        <v>1707673</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3685"/>
+  <dimension ref="A1:F3686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74044,7 +74044,7 @@
         <v>5245.327</v>
       </c>
       <c r="F3681" t="n">
-        <v>2717420</v>
+        <v>2717439</v>
       </c>
     </row>
     <row r="3682">
@@ -74121,10 +74121,30 @@
         <v>5190</v>
       </c>
       <c r="E3685" t="n">
-        <v>5207</v>
+        <v>5205.148</v>
       </c>
       <c r="F3685" t="n">
         <v>1707673</v>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B3686" t="n">
+        <v>5177</v>
+      </c>
+      <c r="C3686" t="n">
+        <v>5194.5</v>
+      </c>
+      <c r="D3686" t="n">
+        <v>5142.5</v>
+      </c>
+      <c r="E3686" t="n">
+        <v>5150</v>
+      </c>
+      <c r="F3686" t="n">
+        <v>2093194</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3686"/>
+  <dimension ref="A1:F3687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74141,10 +74141,30 @@
         <v>5142.5</v>
       </c>
       <c r="E3686" t="n">
-        <v>5150</v>
+        <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093194</v>
+        <v>2093219</v>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B3687" t="n">
+        <v>5155</v>
+      </c>
+      <c r="C3687" t="n">
+        <v>5171</v>
+      </c>
+      <c r="D3687" t="n">
+        <v>5148</v>
+      </c>
+      <c r="E3687" t="n">
+        <v>5165.5</v>
+      </c>
+      <c r="F3687" t="n">
+        <v>1648014</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3687"/>
+  <dimension ref="A1:F3688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093219</v>
+        <v>2093194</v>
       </c>
     </row>
     <row r="3687">
@@ -74161,10 +74161,30 @@
         <v>5148</v>
       </c>
       <c r="E3687" t="n">
-        <v>5165.5</v>
+        <v>5161.758</v>
       </c>
       <c r="F3687" t="n">
         <v>1648014</v>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B3688" t="n">
+        <v>5158</v>
+      </c>
+      <c r="C3688" t="n">
+        <v>5173</v>
+      </c>
+      <c r="D3688" t="n">
+        <v>5145</v>
+      </c>
+      <c r="E3688" t="n">
+        <v>5154</v>
+      </c>
+      <c r="F3688" t="n">
+        <v>1532950</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3688"/>
+  <dimension ref="A1:F3689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093194</v>
+        <v>2093219</v>
       </c>
     </row>
     <row r="3687">
@@ -74181,10 +74181,30 @@
         <v>5145</v>
       </c>
       <c r="E3688" t="n">
-        <v>5154</v>
+        <v>5153.778</v>
       </c>
       <c r="F3688" t="n">
         <v>1532950</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B3689" t="n">
+        <v>5151</v>
+      </c>
+      <c r="C3689" t="n">
+        <v>5170</v>
+      </c>
+      <c r="D3689" t="n">
+        <v>5144</v>
+      </c>
+      <c r="E3689" t="n">
+        <v>5158.22</v>
+      </c>
+      <c r="F3689" t="n">
+        <v>1556203</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3689"/>
+  <dimension ref="A1:F3690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093219</v>
+        <v>2093194</v>
       </c>
     </row>
     <row r="3687">
@@ -74205,6 +74205,26 @@
       </c>
       <c r="F3689" t="n">
         <v>1556203</v>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B3690" t="n">
+        <v>5155</v>
+      </c>
+      <c r="C3690" t="n">
+        <v>5179.5</v>
+      </c>
+      <c r="D3690" t="n">
+        <v>5145.5</v>
+      </c>
+      <c r="E3690" t="n">
+        <v>5165.333</v>
+      </c>
+      <c r="F3690" t="n">
+        <v>1720646</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3690"/>
+  <dimension ref="A1:F3691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093194</v>
+        <v>2093219</v>
       </c>
     </row>
     <row r="3687">
@@ -74225,6 +74225,26 @@
       </c>
       <c r="F3690" t="n">
         <v>1720646</v>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B3691" t="n">
+        <v>5164</v>
+      </c>
+      <c r="C3691" t="n">
+        <v>5232.5</v>
+      </c>
+      <c r="D3691" t="n">
+        <v>5160</v>
+      </c>
+      <c r="E3691" t="n">
+        <v>5214</v>
+      </c>
+      <c r="F3691" t="n">
+        <v>2268200</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -74241,10 +74241,10 @@
         <v>5160</v>
       </c>
       <c r="E3691" t="n">
-        <v>5214</v>
+        <v>5189.5</v>
       </c>
       <c r="F3691" t="n">
-        <v>2268200</v>
+        <v>2612760</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093219</v>
+        <v>2093194</v>
       </c>
     </row>
     <row r="3687">
@@ -74241,10 +74241,10 @@
         <v>5160</v>
       </c>
       <c r="E3691" t="n">
-        <v>5189.5</v>
+        <v>5208.749</v>
       </c>
       <c r="F3691" t="n">
-        <v>2612760</v>
+        <v>2624081</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3691"/>
+  <dimension ref="A1:F3693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74144,7 +74144,7 @@
         <v>5146.559</v>
       </c>
       <c r="F3686" t="n">
-        <v>2093194</v>
+        <v>2093219</v>
       </c>
     </row>
     <row r="3687">
@@ -74245,6 +74245,46 @@
       </c>
       <c r="F3691" t="n">
         <v>2624081</v>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B3692" t="n">
+        <v>5219.5</v>
+      </c>
+      <c r="C3692" t="n">
+        <v>5224.5</v>
+      </c>
+      <c r="D3692" t="n">
+        <v>5194.5</v>
+      </c>
+      <c r="E3692" t="n">
+        <v>5219.393</v>
+      </c>
+      <c r="F3692" t="n">
+        <v>1827866</v>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3693" t="n">
+        <v>5224</v>
+      </c>
+      <c r="C3693" t="n">
+        <v>5235.5</v>
+      </c>
+      <c r="D3693" t="n">
+        <v>5171</v>
+      </c>
+      <c r="E3693" t="n">
+        <v>5183.841</v>
+      </c>
+      <c r="F3693" t="n">
+        <v>2336630</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3693"/>
+  <dimension ref="A1:F3694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74287,6 +74287,26 @@
         <v>2336630</v>
       </c>
     </row>
+    <row r="3694">
+      <c r="A3694" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B3694" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C3694" t="n">
+        <v>5201.5</v>
+      </c>
+      <c r="D3694" t="n">
+        <v>5118</v>
+      </c>
+      <c r="E3694" t="n">
+        <v>5127</v>
+      </c>
+      <c r="F3694" t="n">
+        <v>2648243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3694"/>
+  <dimension ref="A1:F3695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74301,10 +74301,30 @@
         <v>5118</v>
       </c>
       <c r="E3694" t="n">
-        <v>5127</v>
+        <v>5141.176</v>
       </c>
       <c r="F3694" t="n">
         <v>2648243</v>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B3695" t="n">
+        <v>5116</v>
+      </c>
+      <c r="C3695" t="n">
+        <v>5145</v>
+      </c>
+      <c r="D3695" t="n">
+        <v>5101</v>
+      </c>
+      <c r="E3695" t="n">
+        <v>5132.5</v>
+      </c>
+      <c r="F3695" t="n">
+        <v>2253491</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3695"/>
+  <dimension ref="A1:F3696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74321,10 +74321,30 @@
         <v>5101</v>
       </c>
       <c r="E3695" t="n">
-        <v>5132.5</v>
+        <v>5133.174</v>
       </c>
       <c r="F3695" t="n">
         <v>2253491</v>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B3696" t="n">
+        <v>5129.5</v>
+      </c>
+      <c r="C3696" t="n">
+        <v>5171</v>
+      </c>
+      <c r="D3696" t="n">
+        <v>5129.5</v>
+      </c>
+      <c r="E3696" t="n">
+        <v>5156</v>
+      </c>
+      <c r="F3696" t="n">
+        <v>1767670</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -74341,10 +74341,10 @@
         <v>5129.5</v>
       </c>
       <c r="E3696" t="n">
-        <v>5156</v>
+        <v>5158.217</v>
       </c>
       <c r="F3696" t="n">
-        <v>1767670</v>
+        <v>1767684</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3696"/>
+  <dimension ref="A1:F3697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74347,6 +74347,26 @@
         <v>1767684</v>
       </c>
     </row>
+    <row r="3697">
+      <c r="A3697" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B3697" t="n">
+        <v>5137</v>
+      </c>
+      <c r="C3697" t="n">
+        <v>5155</v>
+      </c>
+      <c r="D3697" t="n">
+        <v>5097.5</v>
+      </c>
+      <c r="E3697" t="n">
+        <v>5114</v>
+      </c>
+      <c r="F3697" t="n">
+        <v>2122525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3697"/>
+  <dimension ref="A1:F3698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74361,10 +74361,30 @@
         <v>5097.5</v>
       </c>
       <c r="E3697" t="n">
-        <v>5114</v>
+        <v>5113.595</v>
       </c>
       <c r="F3697" t="n">
         <v>2122525</v>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B3698" t="n">
+        <v>5115.5</v>
+      </c>
+      <c r="C3698" t="n">
+        <v>5139.5</v>
+      </c>
+      <c r="D3698" t="n">
+        <v>5104.5</v>
+      </c>
+      <c r="E3698" t="n">
+        <v>5127.5</v>
+      </c>
+      <c r="F3698" t="n">
+        <v>1857365</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3698"/>
+  <dimension ref="A1:F3699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74381,10 +74381,30 @@
         <v>5104.5</v>
       </c>
       <c r="E3698" t="n">
-        <v>5127.5</v>
+        <v>5134.439</v>
       </c>
       <c r="F3698" t="n">
         <v>1857365</v>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B3699" t="n">
+        <v>5140</v>
+      </c>
+      <c r="C3699" t="n">
+        <v>5170</v>
+      </c>
+      <c r="D3699" t="n">
+        <v>5105.5</v>
+      </c>
+      <c r="E3699" t="n">
+        <v>5127</v>
+      </c>
+      <c r="F3699" t="n">
+        <v>2686509</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3699"/>
+  <dimension ref="A1:F3700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74401,10 +74401,30 @@
         <v>5105.5</v>
       </c>
       <c r="E3699" t="n">
-        <v>5127</v>
+        <v>5122.696</v>
       </c>
       <c r="F3699" t="n">
         <v>2686509</v>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B3700" t="n">
+        <v>5131</v>
+      </c>
+      <c r="C3700" t="n">
+        <v>5155</v>
+      </c>
+      <c r="D3700" t="n">
+        <v>5093.5</v>
+      </c>
+      <c r="E3700" t="n">
+        <v>5145.5</v>
+      </c>
+      <c r="F3700" t="n">
+        <v>2366761</v>
       </c>
     </row>
   </sheetData>
